--- a/common/template/document/generator_schedule.xlsx
+++ b/common/template/document/generator_schedule.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">бюджет!$A$7:$J$8</definedName>
   </definedNames>
-  <calcPr calcId="152511" refMode="R1C1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -66,9 +66,6 @@
     <t>[a.direction_slug]</t>
   </si>
   <si>
-    <t> График работы преподавателей ГБУДО г. Москвы "ДШИ им. И.Ф.Стравинского" на  [doc.plan_year] уч. г.</t>
-  </si>
-  <si>
     <t>понедельник</t>
   </si>
   <si>
@@ -112,6 +109,9 @@
   </si>
   <si>
     <t>[a.level_slug]</t>
+  </si>
+  <si>
+    <t> График работы преподавателей ГБУДО г. Москвы "ДШИ им. И.Ф.Стравинского" на  [doc.plan_year] уч. г. ( [doc.type])</t>
   </si>
 </sst>
 </file>
@@ -269,28 +269,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -299,6 +281,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,7 +568,7 @@
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -591,49 +591,49 @@
       <c r="J5" s="8"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="E6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
     </row>
     <row r="7" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="13" t="s">
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="H7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="I7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="J7" s="10" t="s">
         <v>15</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -641,31 +641,31 @@
         <v>8</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="G8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="H8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="I8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="J8" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -693,8 +693,8 @@
       <c r="G11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>

--- a/common/template/document/generator_schedule.xlsx
+++ b/common/template/document/generator_schedule.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OSPanel\domains\ais-dsi.loc\common\template\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OSPanel\domains\ais-dsi-2.loc\common\template\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="бюджет" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">бюджет!$A$7:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">бюджет!$A$8:$J$9</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -111,7 +111,7 @@
     <t>[a.level_slug]</t>
   </si>
   <si>
-    <t> График работы преподавателей ГБУДО г. Москвы "ДШИ им. И.Ф.Стравинского" на  [doc.plan_year] уч. г. ( [doc.type])</t>
+    <t> График работы преподавателей ГБУДО г. Москвы "ДШИ им. И.Ф.Стравинского" на  [doc.plan_year] уч. г.  ([doc.type])</t>
   </si>
 </sst>
 </file>
@@ -167,7 +167,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -245,11 +245,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -288,10 +301,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -524,14 +543,14 @@
   <sheetPr codeName="Лист1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="43" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
-    <col min="5" max="10" width="20.7109375" style="1" customWidth="1"/>
+    <col min="5" max="10" width="24.85546875" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="13.7109375" style="1" customWidth="1"/>
     <col min="13" max="13" width="12.85546875" style="1" customWidth="1"/>
@@ -579,103 +598,105 @@
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C7" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D7" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-    </row>
-    <row r="7" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+    </row>
+    <row r="8" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J8" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G9" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J9" s="13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
@@ -685,41 +706,50 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="K10" s="5"/>
-      <c r="Q10" s="5"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="G11" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="K11" s="5"/>
+      <c r="Q11" s="5"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="K12" s="5"/>
-      <c r="Q12" s="5"/>
+      <c r="G12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
+      <c r="K13" s="5"/>
+      <c r="Q13" s="5"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H15" s="4"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H20" s="4"/>
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H16" s="4"/>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H21" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:J7"/>
   </mergeCells>
   <pageMargins left="0.70000004768371604" right="0.70000004768371604" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/common/template/document/generator_schedule.xlsx
+++ b/common/template/document/generator_schedule.xlsx
@@ -15,7 +15,7 @@
     <sheet name="бюджет" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">бюджет!$A$8:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">бюджет!$A$8:$I$9</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>№</t>
   </si>
   <si>
-    <t>категория</t>
-  </si>
-  <si>
     <t>долж.</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
   </si>
   <si>
     <t>[a.fullname]</t>
-  </si>
-  <si>
-    <t>[a.level_slug]</t>
   </si>
   <si>
     <t> График работы преподавателей ГБУДО г. Москвы "ДШИ им. И.Ф.Стравинского" на  [doc.plan_year] уч. г.  ([doc.type])</t>
@@ -147,7 +141,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,13 +150,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -273,51 +261,49 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -543,51 +529,50 @@
   <sheetPr codeName="Лист1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="43" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
-    <col min="5" max="10" width="24.85546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="1" customWidth="1"/>
-    <col min="14" max="15" width="11.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.42578125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="9" width="24.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" style="1" customWidth="1"/>
+    <col min="13" max="14" width="11.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I1" s="1" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="5"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="5"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="5"/>
-      <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J2" s="5"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="P3" s="5"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -595,9 +580,8 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -606,150 +590,138 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:16" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="20" t="s">
+      <c r="B9" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-    </row>
-    <row r="8" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="K11" s="5"/>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J11" s="5"/>
+      <c r="P11" s="5"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="G12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="K13" s="5"/>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J13" s="5"/>
+      <c r="P13" s="5"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H16" s="4"/>
-    </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H21" s="4"/>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G16" s="4"/>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:J7"/>
+    <mergeCell ref="D7:I7"/>
   </mergeCells>
   <pageMargins left="0.70000004768371604" right="0.70000004768371604" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>
